--- a/real_estate_forms/025_property_rental_agreement_intake_form--real_estate_forms.xlsx
+++ b/real_estate_forms/025_property_rental_agreement_intake_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'month_to_month'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 'month_to_month'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'week_to_week'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 'week_to_week'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'month_to_month_fixed'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'month_to_month_fixed'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'signed'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'signed'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'unsigned'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'unsigned'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_none}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': None}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_none}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': None}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'apartment'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'apartment'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'house'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'house'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'condominium'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'condominium'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'other'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'approved'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'approved'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'pending'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'pending'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_'rejected'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 'rejected'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_'active'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': 'active'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_'inactive'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': 'inactive'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_'expired'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': 'expired'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option':_'active'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option': 'active'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option':_'inactive'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option': 'inactive'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option':_'expired'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option': 'expired'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option':_none}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option': None}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option':_'air_conditioning'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option': 'air_conditioning'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option':_'balcony'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option': 'balcony'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option':_'balcony_furniture'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option': 'balcony_furniture'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option':_'elevator'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option': 'elevator'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option':_'fire_place'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option': 'fire_place'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option':_'fireplace'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option': 'fireplace'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option':_none}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option': None}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'option':_none}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'option': None}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'option':_none}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'option': None}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'option':_'rented'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'option': 'rented'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'option':_'available'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'option': 'available'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'option':_none}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'option': None}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'option':_'weekly'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'option': 'weekly'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'option':_'bi_weekly'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'option': 'bi_weekly'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'option':_'monthly'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'option': 'monthly'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'option':_'weekly'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'option': 'weekly'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1839,12 +1839,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'option':_'bi_weekly'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'option': 'bi_weekly'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'option':_'monthly'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'option': 'monthly'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
